--- a/excel_files/3.3.3.xlsx
+++ b/excel_files/3.3.3.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93101088-B9AA-4085-A715-A33454B931F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12435" yWindow="885" windowWidth="13050" windowHeight="12990"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="37">
   <si>
     <t>Кыргызская Республика</t>
   </si>
@@ -130,7 +131,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -280,22 +281,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -304,16 +301,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -325,40 +319,31 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -367,22 +352,33 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="2"/>
-    <cellStyle name="Обычный 6" xfId="3"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -398,9 +394,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -438,9 +434,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -475,7 +471,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -510,7 +506,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -683,15 +679,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="33.42578125" customWidth="1"/>
     <col min="4" max="4" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -701,715 +697,738 @@
       <c r="C1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="U2" s="27"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="17">
         <v>2007</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="17">
         <v>2008</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="17">
         <v>2009</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="17">
         <v>2010</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="17">
         <v>2011</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="17">
         <v>2012</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="17">
         <v>2013</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="17">
         <v>2014</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="17">
         <v>2015</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="17">
         <v>2016</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="17">
         <v>2017</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="17">
         <v>2018</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="17">
         <v>2019</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="17">
         <v>2020</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="17">
         <v>2021</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="17">
         <v>2022</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="17">
         <v>2023</v>
       </c>
+      <c r="U3" s="28">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="18">
         <v>1.8436578171091445E-2</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="18">
         <v>3.4284819615183378E-3</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="18">
         <v>7.4304183121173221E-4</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="18">
         <v>3.6710989067467454E-4</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="18">
         <v>7.9785970507478664E-3</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="18">
         <v>5.3499672136175921E-4</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="24">
         <v>6.9931879356319008E-4</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="24">
+      <c r="K4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="18">
         <v>1.6786209658751467E-4</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="18">
         <v>9.8686807547567032E-4</v>
       </c>
-      <c r="N4" s="25">
+      <c r="N4" s="19">
         <v>3.2266052966339247E-4</v>
       </c>
-      <c r="O4" s="25">
+      <c r="O4" s="19">
         <v>1.5814989921897674E-4</v>
       </c>
-      <c r="P4" s="25">
+      <c r="P4" s="19">
         <v>1.5814989921897674E-4</v>
       </c>
-      <c r="Q4" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="25">
+      <c r="Q4" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="19">
         <v>2.9886145739191973E-4</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="19">
         <v>0</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="19">
         <v>0</v>
       </c>
+      <c r="U4" s="29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="20">
         <v>5.181615627752733E-2</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="20">
         <v>4.6674227891585103E-3</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="20">
         <v>6.9694991485595211E-3</v>
       </c>
-      <c r="G5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="27" t="s">
+      <c r="G5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="20">
         <v>6.1413932978974942E-3</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="20">
         <v>1.0130655058286724E-3</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="20">
         <v>9.8526923959875901E-4</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="20">
         <v>1.9419587372607506E-3</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="27" t="s">
+      <c r="H6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="20">
         <v>0</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="20">
         <v>0</v>
       </c>
-      <c r="F7" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="26">
+      <c r="F7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="20">
         <v>2.2188003390326921E-3</v>
       </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="27" t="s">
+      <c r="J7" s="20"/>
+      <c r="K7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="20">
         <v>3.7139514586544352E-3</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="20">
         <v>3.6949316622389068E-3</v>
       </c>
-      <c r="F8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="27" t="s">
+      <c r="F8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="26">
+      <c r="D9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20">
         <v>0</v>
       </c>
-      <c r="F9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="26">
+      <c r="F9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="20">
         <v>8.777173030555973E-4</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="27" t="s">
+      <c r="I9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="20">
         <v>0</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="20">
         <v>0</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="27" t="s">
+      <c r="F10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="20">
         <v>3.1648490762596758E-2</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="20">
         <v>5.2546950700450854E-3</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="26">
+      <c r="F11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="20">
         <v>1.2041504658256077E-3</v>
       </c>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="26">
+      <c r="J11" s="20"/>
+      <c r="K11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="20">
         <v>1.1156617715147004E-3</v>
       </c>
-      <c r="N11" s="27">
+      <c r="N11" s="21">
         <v>0</v>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="21">
         <v>1.0736179852484889E-3</v>
       </c>
-      <c r="P11" s="27">
+      <c r="P11" s="21">
         <v>9.6100251782659671E-2</v>
       </c>
-      <c r="Q11" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="27">
+      <c r="Q11" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="21">
         <v>0</v>
       </c>
-      <c r="T11" s="27" t="s">
+      <c r="T11" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="25">
         <v>5.1834957495334857E-2</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="20">
         <v>1.2209878035528303E-2</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="26">
+      <c r="F12" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="20">
         <v>4.7285359068870547E-2</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="20">
         <v>1.1306384941704281E-3</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="20">
         <v>4.4193425785980078E-3</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="26">
+      <c r="K12" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="20">
         <v>1.054953587316926E-3</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="20">
         <v>3.0946498661563932E-3</v>
       </c>
-      <c r="N12" s="27">
+      <c r="N12" s="21">
         <v>2.0176402285179327E-3</v>
       </c>
-      <c r="O12" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="32">
+      <c r="O12" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="26">
         <v>1.8411781330637848E-3</v>
       </c>
-      <c r="S12" s="32">
+      <c r="S12" s="26">
         <v>1.8411781330637848E-3</v>
       </c>
-      <c r="T12" s="32">
+      <c r="T12" s="26">
         <v>1.731197036190674E-3</v>
       </c>
+      <c r="U12" s="32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="22">
         <v>4.0037475076671767E-3</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="22">
         <v>0</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="28">
+      <c r="F13" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="22">
         <v>7.172572084349447E-3</v>
       </c>
-      <c r="N13" s="29">
+      <c r="N13" s="23">
         <v>0</v>
       </c>
-      <c r="O13" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="29" t="s">
+      <c r="O13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="U13" s="31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
